--- a/results/soae_T_xi [int 25ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
+++ b/results/soae_T_xi [int 25ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0128086725869176</v>
+        <v>0.01280905648166397</v>
       </c>
       <c r="F2" t="n">
         <v>10.09595355218707</v>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.01144864713420626</v>
+        <v>0.01146188566518024</v>
       </c>
       <c r="F3" t="n">
         <v>10.09595355218707</v>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.02317369967990051</v>
+        <v>0.02317268472793207</v>
       </c>
       <c r="F4" t="n">
         <v>3.09945385050024</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.02176788171687337</v>
+        <v>0.02177175900757706</v>
       </c>
       <c r="F5" t="n">
         <v>3.09945385050024</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.02485361071059479</v>
+        <v>0.02485418200884865</v>
       </c>
       <c r="F6" t="n">
         <v>0.8253318426568844</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.02486043121220602</v>
+        <v>0.02486561525224982</v>
       </c>
       <c r="F7" t="n">
         <v>0.8253318426568844</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.02402277041517802</v>
+        <v>0.02402693684665887</v>
       </c>
       <c r="F8" t="n">
         <v>2.212581609474567</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.02339276922187955</v>
+        <v>0.02339822055989159</v>
       </c>
       <c r="F9" t="n">
         <v>2.212581609474567</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.02319566011072066</v>
+        <v>0.02319368543035152</v>
       </c>
       <c r="F10" t="n">
         <v>1.306834054289299</v>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02273525432407291</v>
+        <v>0.02273839756067757</v>
       </c>
       <c r="F11" t="n">
         <v>1.306834054289299</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.02484923093206384</v>
+        <v>0.02484993859461844</v>
       </c>
       <c r="F12" t="n">
         <v>1.226981092761272</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.02487078534870558</v>
+        <v>0.02487596307811651</v>
       </c>
       <c r="F13" t="n">
         <v>1.226981092761272</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0229317189743448</v>
+        <v>0.0229297696061082</v>
       </c>
       <c r="F14" t="n">
         <v>2.396894500224019</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.02175467416729787</v>
+        <v>0.02174848247002179</v>
       </c>
       <c r="F15" t="n">
         <v>2.396894500224019</v>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.02475215597389021</v>
+        <v>0.02475271444643159</v>
       </c>
       <c r="F16" t="n">
         <v>1.618801456042487</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.02415873326174273</v>
+        <v>0.02416223905414184</v>
       </c>
       <c r="F17" t="n">
         <v>1.618801456042487</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0242026173212002</v>
+        <v>0.02420481862761872</v>
       </c>
       <c r="F18" t="n">
         <v>0.8820415846920716</v>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.02417705418909976</v>
+        <v>0.02418497401175439</v>
       </c>
       <c r="F19" t="n">
         <v>0.8820415846920716</v>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.02318695597002828</v>
+        <v>0.02319139499628461</v>
       </c>
       <c r="F20" t="n">
         <v>2.415225068705968</v>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.02237571394087015</v>
+        <v>0.02238127217556884</v>
       </c>
       <c r="F21" t="n">
         <v>2.415225068705968</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.02449250568285679</v>
+        <v>0.02449258524972188</v>
       </c>
       <c r="F22" t="n">
         <v>1.281367686769816</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.02456537487541001</v>
+        <v>0.02456910239000408</v>
       </c>
       <c r="F23" t="n">
         <v>1.281367686769816</v>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0127336917192973</v>
+        <v>0.01272950639492331</v>
       </c>
       <c r="F24" t="n">
         <v>10.05992016213009</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.01110927528766888</v>
+        <v>0.0111212161576389</v>
       </c>
       <c r="F25" t="n">
         <v>10.05992016213009</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.02407919220276717</v>
+        <v>0.02408215294275247</v>
       </c>
       <c r="F26" t="n">
         <v>0.8440441282866774</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.02386044635024903</v>
+        <v>0.02387366154151819</v>
       </c>
       <c r="F27" t="n">
         <v>0.8440441282866774</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.02453196971267964</v>
+        <v>0.02453243753113031</v>
       </c>
       <c r="F28" t="n">
         <v>1.254614652958397</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0245615190184612</v>
+        <v>0.02456637388630136</v>
       </c>
       <c r="F29" t="n">
         <v>1.254614652958397</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.02206661249346151</v>
+        <v>0.02206618888877734</v>
       </c>
       <c r="F30" t="n">
         <v>4.481984426888731</v>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.02059376827824283</v>
+        <v>0.0206061477328768</v>
       </c>
       <c r="F31" t="n">
         <v>4.481984426888731</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.02294991451604413</v>
+        <v>0.02294604952104086</v>
       </c>
       <c r="F32" t="n">
         <v>1.621707514273231</v>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.02168854415341243</v>
+        <v>0.02168542703219013</v>
       </c>
       <c r="F33" t="n">
         <v>1.621707514273231</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.01461663064376069</v>
+        <v>0.01461895803636343</v>
       </c>
       <c r="F34" t="n">
         <v>11.8803921636882</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.01441934544221997</v>
+        <v>0.01444141530814852</v>
       </c>
       <c r="F35" t="n">
         <v>11.8803921636882</v>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.003777906875230875</v>
+        <v>0.003777116572294734</v>
       </c>
       <c r="F36" t="n">
         <v>40.81661019133534</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.003381100035469546</v>
+        <v>0.003386037605755201</v>
       </c>
       <c r="F37" t="n">
         <v>40.81661019133534</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0101387670166837</v>
+        <v>0.0101361223857065</v>
       </c>
       <c r="F38" t="n">
         <v>19.05817478384657</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.01002220505113034</v>
+        <v>0.01002910757552835</v>
       </c>
       <c r="F39" t="n">
         <v>19.05817478384657</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.004931855759117072</v>
+        <v>0.004929799878765024</v>
       </c>
       <c r="F40" t="n">
         <v>33.25889734469793</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.004708948096931038</v>
+        <v>0.004712487894096316</v>
       </c>
       <c r="F41" t="n">
         <v>33.25889734469793</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.009574353295989794</v>
+        <v>0.009573828884065848</v>
       </c>
       <c r="F42" t="n">
         <v>16.38970637248534</v>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.009236599664134541</v>
+        <v>0.009249031185795252</v>
       </c>
       <c r="F43" t="n">
         <v>16.38970637248534</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.004753686375963083</v>
+        <v>0.004753633068745605</v>
       </c>
       <c r="F44" t="n">
         <v>30.52335899097242</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.004242589116572662</v>
+        <v>0.004248286146416775</v>
       </c>
       <c r="F45" t="n">
         <v>30.52335899097242</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.007906057422992076</v>
+        <v>0.007908172358770131</v>
       </c>
       <c r="F46" t="n">
         <v>24.19350636189434</v>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.007822789216384603</v>
+        <v>0.007833518565704439</v>
       </c>
       <c r="F47" t="n">
         <v>24.19350636189434</v>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.004350824900194551</v>
+        <v>0.004349012710847043</v>
       </c>
       <c r="F48" t="n">
         <v>42.70877068563502</v>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.00429524013924533</v>
+        <v>0.004296599240245753</v>
       </c>
       <c r="F49" t="n">
         <v>42.70877068563502</v>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.006221410820367656</v>
+        <v>0.006221710514842789</v>
       </c>
       <c r="F50" t="n">
         <v>22.02734034403161</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.005673412098495022</v>
+        <v>0.005683647127923793</v>
       </c>
       <c r="F51" t="n">
         <v>22.02734034403161</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.01289283375736971</v>
+        <v>0.01288524072227612</v>
       </c>
       <c r="F52" t="n">
         <v>14.68264699299626</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.01289224094404842</v>
+        <v>0.01289761955374856</v>
       </c>
       <c r="F53" t="n">
         <v>14.68264699299626</v>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.007409910606416587</v>
+        <v>0.007410236667083622</v>
       </c>
       <c r="F54" t="n">
         <v>26.1281172770193</v>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.007390772765079308</v>
+        <v>0.007400299398675495</v>
       </c>
       <c r="F55" t="n">
         <v>26.1281172770193</v>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.007545948591311131</v>
+        <v>0.007554150607074006</v>
       </c>
       <c r="F56" t="n">
         <v>24.43832250664904</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0073521530592547</v>
+        <v>0.007368072810511313</v>
       </c>
       <c r="F57" t="n">
         <v>24.43832250664904</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.00781684438590324</v>
+        <v>0.007813582511765756</v>
       </c>
       <c r="F58" t="n">
         <v>25.14257025564731</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.007314540684355826</v>
+        <v>0.007317517594240585</v>
       </c>
       <c r="F59" t="n">
         <v>25.14257025564731</v>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.002930444451046209</v>
+        <v>0.002931137256803178</v>
       </c>
       <c r="F60" t="n">
         <v>64.87424396895483</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.00261333343395594</v>
+        <v>0.002617372072465359</v>
       </c>
       <c r="F61" t="n">
         <v>64.87424396895483</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.003244868988575032</v>
+        <v>0.00324531031949485</v>
       </c>
       <c r="F62" t="n">
         <v>48.24737092155696</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.002885745273693652</v>
+        <v>0.002891319178258152</v>
       </c>
       <c r="F63" t="n">
         <v>48.24737092155696</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.003598633339848247</v>
+        <v>0.003598089485354101</v>
       </c>
       <c r="F64" t="n">
         <v>42.07107102770869</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.003147346160064153</v>
+        <v>0.003151738249718821</v>
       </c>
       <c r="F65" t="n">
         <v>42.07107102770869</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.00378726473904875</v>
+        <v>0.003785882713939159</v>
       </c>
       <c r="F66" t="n">
         <v>40.32418949488441</v>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.003378596949663832</v>
+        <v>0.003382524157873764</v>
       </c>
       <c r="F67" t="n">
         <v>40.32418949488441</v>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.00716679444166818</v>
+        <v>0.00716898416765276</v>
       </c>
       <c r="F68" t="n">
         <v>21.79457757467633</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.006629138359004715</v>
+        <v>0.006641488961851903</v>
       </c>
       <c r="F69" t="n">
         <v>21.79457757467633</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.00436097406066016</v>
+        <v>0.00435988515085583</v>
       </c>
       <c r="F70" t="n">
         <v>35.27900051644691</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.003962256355156162</v>
+        <v>0.003968058800159983</v>
       </c>
       <c r="F71" t="n">
         <v>35.27900051644691</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.009914607070866751</v>
+        <v>0.009913305503909991</v>
       </c>
       <c r="F72" t="n">
         <v>15.48239598695274</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.009711713406162335</v>
+        <v>0.009722984389178915</v>
       </c>
       <c r="F73" t="n">
         <v>15.48239598695274</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.005328768724059758</v>
+        <v>0.005327806851231235</v>
       </c>
       <c r="F74" t="n">
         <v>26.01227642789845</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.004639419822555075</v>
+        <v>0.004644978038050532</v>
       </c>
       <c r="F75" t="n">
         <v>26.01227642789845</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.005628228801831114</v>
+        <v>0.005627945864613421</v>
       </c>
       <c r="F76" t="n">
         <v>24.55723338600139</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.004994823349792234</v>
+        <v>0.004999640569191189</v>
       </c>
       <c r="F77" t="n">
         <v>24.55723338600139</v>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.007502718934668381</v>
+        <v>0.007506550662754104</v>
       </c>
       <c r="F78" t="n">
         <v>23.555089386247</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.007029177809720508</v>
+        <v>0.007042669413807965</v>
       </c>
       <c r="F79" t="n">
         <v>23.555089386247</v>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.004689293675744767</v>
+        <v>0.004689313780698281</v>
       </c>
       <c r="F80" t="n">
         <v>30.94992821931555</v>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.004206765921042821</v>
+        <v>0.004210445263881694</v>
       </c>
       <c r="F81" t="n">
         <v>30.94992821931555</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.008833317389401877</v>
+        <v>0.008833730561530301</v>
       </c>
       <c r="F82" t="n">
         <v>17.11041974211544</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.008036879632794069</v>
+        <v>0.008040564718660843</v>
       </c>
       <c r="F83" t="n">
         <v>17.11041974211544</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.005448985355417038</v>
+        <v>0.00544767509730626</v>
       </c>
       <c r="F84" t="n">
         <v>25.09099671696914</v>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.004731484891480332</v>
+        <v>0.004735985415064106</v>
       </c>
       <c r="F85" t="n">
         <v>25.09099671696914</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.003138861775412451</v>
+        <v>0.003138257179598815</v>
       </c>
       <c r="F86" t="n">
         <v>56.10647072185828</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.002681199047820776</v>
+        <v>0.002684736887935146</v>
       </c>
       <c r="F87" t="n">
         <v>56.10647072185828</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.006398245155821713</v>
+        <v>0.006398721259582722</v>
       </c>
       <c r="F88" t="n">
         <v>26.61131083407046</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.006004737785869457</v>
+        <v>0.00601436113653451</v>
       </c>
       <c r="F89" t="n">
         <v>26.61131083407046</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.009185103850060324</v>
+        <v>0.009193494677807812</v>
       </c>
       <c r="F90" t="n">
         <v>17.17910082644781</v>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.008517429847385726</v>
+        <v>0.008533990136220094</v>
       </c>
       <c r="F91" t="n">
         <v>17.17910082644781</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.00367248127330779</v>
+        <v>0.00367474798509997</v>
       </c>
       <c r="F92" t="n">
         <v>41.33077231855378</v>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.003197504071403861</v>
+        <v>0.003203738526235381</v>
       </c>
       <c r="F93" t="n">
         <v>41.33077231855378</v>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.004547494719726909</v>
+        <v>0.004545744760596944</v>
       </c>
       <c r="F94" t="n">
         <v>31.93359446629537</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00404233602702011</v>
+        <v>0.004048217659962053</v>
       </c>
       <c r="F95" t="n">
         <v>31.93359446629537</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.004836781339521391</v>
+        <v>0.00483768870901634</v>
       </c>
       <c r="F96" t="n">
         <v>35.1035288170361</v>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.004366798616346796</v>
+        <v>0.004374714331938496</v>
       </c>
       <c r="F97" t="n">
         <v>35.1035288170361</v>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.002358534951493008</v>
+        <v>0.002358574984397322</v>
       </c>
       <c r="F98" t="n">
         <v>70.42713629849885</v>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.002023652769176554</v>
+        <v>0.002027775437431392</v>
       </c>
       <c r="F99" t="n">
         <v>70.42713629849885</v>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.003206110902282595</v>
+        <v>0.003204839758868071</v>
       </c>
       <c r="F100" t="n">
         <v>48.09727907943265</v>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.002770546023085702</v>
+        <v>0.002774968663731538</v>
       </c>
       <c r="F101" t="n">
         <v>48.09727907943265</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.003283235302984103</v>
+        <v>0.003283330957571337</v>
       </c>
       <c r="F102" t="n">
         <v>48.35560222806118</v>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.002888209912600668</v>
+        <v>0.002891574596444722</v>
       </c>
       <c r="F103" t="n">
         <v>48.35560222806118</v>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.004335688775815345</v>
+        <v>0.004335962912721367</v>
       </c>
       <c r="F104" t="n">
         <v>41.34715232351992</v>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.003826236455285618</v>
+        <v>0.003833406576458869</v>
       </c>
       <c r="F105" t="n">
         <v>41.34715232351992</v>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.003197338901247641</v>
+        <v>0.003197133649905171</v>
       </c>
       <c r="F106" t="n">
         <v>48.82276869525922</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.002769865255658493</v>
+        <v>0.002774406350262305</v>
       </c>
       <c r="F107" t="n">
         <v>48.82276869525922</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.004704682024285276</v>
+        <v>0.004703863602421923</v>
       </c>
       <c r="F108" t="n">
         <v>34.72295925128499</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.004112194194600164</v>
+        <v>0.004114808463926451</v>
       </c>
       <c r="F109" t="n">
         <v>34.72295925128499</v>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.004129066367033645</v>
+        <v>0.004128738070369161</v>
       </c>
       <c r="F110" t="n">
         <v>43.26334017048392</v>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.003604292529904621</v>
+        <v>0.003610326862126191</v>
       </c>
       <c r="F111" t="n">
         <v>43.26334017048392</v>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.001892290730645961</v>
+        <v>0.001891389444991333</v>
       </c>
       <c r="F112" t="n">
         <v>91.05438059951148</v>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.0016372156721773</v>
+        <v>0.001638927234775874</v>
       </c>
       <c r="F113" t="n">
         <v>91.05438059951148</v>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.005400596406702775</v>
+        <v>0.005401542952690689</v>
       </c>
       <c r="F114" t="n">
         <v>29.15344518718943</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.004708609741943886</v>
+        <v>0.004714653759482075</v>
       </c>
       <c r="F115" t="n">
         <v>29.15344518718943</v>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.003477616025253666</v>
+        <v>0.003477709660665875</v>
       </c>
       <c r="F116" t="n">
         <v>49.72373786348046</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.003005142453372486</v>
+        <v>0.003010092753678733</v>
       </c>
       <c r="F117" t="n">
         <v>49.72373786348046</v>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.009155863862788089</v>
+        <v>0.009155480536615902</v>
       </c>
       <c r="F118" t="n">
         <v>19.85800760568668</v>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.008526359752519449</v>
+        <v>0.008534965490585002</v>
       </c>
       <c r="F119" t="n">
         <v>19.85800760568668</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.003567567975448407</v>
+        <v>0.003564768314869315</v>
       </c>
       <c r="F120" t="n">
         <v>44.79676977747089</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.003126573764615127</v>
+        <v>0.003129116566094696</v>
       </c>
       <c r="F121" t="n">
         <v>44.79676977747089</v>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.002043194121637568</v>
+        <v>0.002043237253150163</v>
       </c>
       <c r="F122" t="n">
         <v>86.85132295553052</v>
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.001730944917916101</v>
+        <v>0.001735151543761856</v>
       </c>
       <c r="F123" t="n">
         <v>86.85132295553052</v>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.02243018175724446</v>
+        <v>0.02242786444720904</v>
       </c>
       <c r="F124" t="n">
         <v>5.437958953595492</v>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.02155476540528656</v>
+        <v>0.02156311297883979</v>
       </c>
       <c r="F125" t="n">
         <v>5.437958953595492</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.003342850102324404</v>
+        <v>0.003346456918777798</v>
       </c>
       <c r="F126" t="n">
         <v>47.57406740201719</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.00289061761455977</v>
+        <v>0.002898581966173531</v>
       </c>
       <c r="F127" t="n">
         <v>47.57406740201719</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.01546091181242632</v>
+        <v>0.01544880056137418</v>
       </c>
       <c r="F128" t="n">
         <v>11.3439055252793</v>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.01465760932254628</v>
+        <v>0.01466395076259594</v>
       </c>
       <c r="F129" t="n">
         <v>11.3439055252793</v>

--- a/results/soae_T_xi [int 25ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
+++ b/results/soae_T_xi [int 25ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E128" t="n">
